--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -494,10 +494,10 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -517,10 +517,10 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="15" customWidth="1" min="38" max="38"/>
@@ -534,7 +534,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,10 +851,8 @@
           <t>Sunjeet lama</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841451281</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841451281</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9808074911</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9808074911</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.71621</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.71621</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -944,50 +938,257 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L53-5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.368</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.36799999999999</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 35m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381154</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Anil Kumar</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Anil Kumar</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9815730689</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9886262513</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:45:39 AM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.71748</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Near CHABAHIL PLAZA, Ring Road Chowk, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>samjhanagurung696@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>20:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L13-7</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.3476</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 35m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2d 16m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1010,12 +1211,12 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1039,7 +1240,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1049,7 +1250,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1060,7 +1261,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1273,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1285,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2d 16m</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1326,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1183,14 +1384,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1266,6 +1467,73 @@
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381154</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Anil Kumar</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:45:39 AM</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>2d 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1048,10 +1048,8 @@
           <t>Anil Kumar</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9815730689</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9815730689</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1066,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9886262513</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9886262513</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1086,10 +1082,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.71748</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.71748</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1145,25 +1139,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L13-7</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.3476</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.3476</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1212,7 +1202,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1503,7 +1493,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,12 +483,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1179,6 +1179,635 @@
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381073</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:40:01 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.69469</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Maitighar Mandala -11, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>sagarsaridhungana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>21:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.32052</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:32 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381073</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:40:01 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.69469</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Maitighar Mandala -11, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>sagarsaridhungana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>21:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.32052</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381115</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9863593473</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:30:32 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9863593473</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:13:54 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:30:32 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.703184</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>ASPHODEL PUBLIC SCHOOL - Private educational institution P83G+2XM Kathmandu 44600, Bagmati, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>suryathapa4301@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB206</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.32805</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1202,7 +1831,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1230,7 +1859,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1240,7 +1869,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1251,7 +1880,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1904,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 16m</t>
+          <t>2d 1h 24m</t>
         </is>
       </c>
     </row>
@@ -1316,14 +1945,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1374,14 +2003,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1524,6 +2153,140 @@
       <c r="M18" s="3" t="inlineStr">
         <is>
           <t>2d 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TKT1381073</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:40:01 AM</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381073</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:40:01 AM</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1249,10 +1249,8 @@
           <t>Sagar Dhungana</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1267,10 +1265,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1287,10 +1283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.69469</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.69469</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1346,25 +1340,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.32052</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.32052</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1460,10 +1450,8 @@
           <t>Sagar Dhungana</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1478,10 +1466,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1498,10 +1484,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.69469</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.69469</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1557,25 +1541,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.32052</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.32052</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1671,10 +1651,8 @@
           <t>Surya Bahadur Thapa</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9863593473</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9863593473</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1689,10 +1667,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9863593473</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9863593473</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1709,10 +1685,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.703184</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.703184</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1764,48 +1738,147 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>CDB206</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.32805</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.32805</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 16m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1822,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1831,7 +1904,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1859,7 +1932,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1953,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1956,335 +2029,364 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>TKT1381154</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Anil Kumar</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 11:45:39 AM</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>2d 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TKT1381073</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Sagar Dhungana</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:40:01 AM</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>TKT1381154</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Anil Kumar</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:45:39 AM</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>2d 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>TKT1381073</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Sagar Dhungana</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:40:01 AM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381073</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:40:01 AM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>2d 1h 57m</t>
         </is>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,13 +483,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -513,7 +513,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -524,12 +524,12 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1884,6 +1884,416 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381027</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860037533</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:27:50 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860037533</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:04:31 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:27:50 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.765228</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Deko fairocha, Kathmandu 44600 Near by Tokha SB Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>shrsuresh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>23:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L25-8</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.327917</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 23m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:24 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382665</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9840562307</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9844208629</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:24:53 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Radheradhe, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9844208629@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L61-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1895,7 +2305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1904,7 +2314,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1932,7 +2342,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1942,7 +2352,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1977,7 +2387,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 24m</t>
+          <t>2d 1h 53m</t>
         </is>
       </c>
     </row>
@@ -2018,14 +2428,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -2090,14 +2500,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -2392,6 +2802,73 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1381027</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Suresh Shrestha</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:27:50 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:04:31 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:27:50 PM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2d 3h 23m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1951,10 +1951,8 @@
           <t>Suresh Shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860037533</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860037533</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -1969,10 +1967,8 @@
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>9860037533</t>
-        </is>
+      <c r="U8" s="3" t="n">
+        <v>9860037533</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1989,10 +1985,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.765228</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.765228</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2048,25 +2042,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L25-8</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.327917</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.327917</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2162,10 +2152,8 @@
           <t>Hemanta bhandari</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9840562307</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9840562307</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2180,10 +2168,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>9844208629</t>
-        </is>
+      <c r="U9" s="3" t="n">
+        <v>9844208629</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -2251,10 +2237,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2265,30 +2249,443 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>23h 42m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>23h 42m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:44 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:40 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:36 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381392</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Ambar  kumar magar</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Ambar  kumar magar</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841302840</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:39:15 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841302840</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:39:15 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.75076</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Bihanai basti, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>18:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L61-6</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2305,7 +2702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2342,7 +2739,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2352,7 +2749,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2363,7 +2760,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2772,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>9h 23m</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2784,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 53m</t>
+          <t>2d 1h 18m</t>
         </is>
       </c>
     </row>
@@ -2428,14 +2825,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2500,14 +2897,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2835,14 +3232,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>30 Oct 2026 01:27:50 PM</t>
@@ -2866,6 +3263,73 @@
       <c r="M23" s="5" t="inlineStr">
         <is>
           <t>2d 3h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381392</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Ambar  kumar magar</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:39:15 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:39:15 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 57m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 57m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2551,10 +2551,8 @@
           <t>Ambar  kumar magar</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841302840</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841302840</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2569,10 +2567,8 @@
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>9841302840</t>
-        </is>
+      <c r="U12" s="3" t="n">
+        <v>9841302840</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2589,10 +2585,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.75076</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.75076</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2644,25 +2638,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L61-6</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2711,7 +2701,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3299,7 +3289,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2681,6 +2681,1045 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382962</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Biphute</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Biphute</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9705259533</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:31 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>LTP9705259533</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:40:21 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:31 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>27.671718509307166, 85.31908851642197 GPS Coordinates Nearest: LTP003-01-4/13-L113 (28m Road) Map: C</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>9705259533@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>07:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L113-2</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>renewal wifi6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381122</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Arbin Thakur</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Arbin Thakur</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9802100149</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:07:58 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9802100149</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:19:57 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:07:58 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.65685</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Near Imadol Police Station lalitpur mahalaxmi , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>arbin.th2012@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>22:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3448</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1383657</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Shrestha</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Shrestha</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9863481720</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:33 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9863481720</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:01:37 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:33 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Near Euro School Ganesh Chowk, New Colony, Hattigauda Budhanilkantha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>sujaldon27@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>01:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L59-8</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381219</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9843560015</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9818852660</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:35:16 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.71774</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Prime College,Pahikwo Sadak, Kathmandu 44600,27.71696, 85.30267 - Prime College,Pahikwo Sadak, Kathm</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>sayarkhadka@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>21:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.3018</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 18m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:52 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382043</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Budhathoki</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Budhathoki</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9803166523</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9803166523</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 07:47:21 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.705262</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near to Basantapur Sekuwa,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>budhathokimanoj12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>13:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB286</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.305828</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 5m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2692,7 +3731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2701,7 +3740,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2729,7 +3768,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2739,7 +3778,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2750,7 +3789,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2762,7 +3801,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 23m</t>
+          <t>4h 41m</t>
         </is>
       </c>
     </row>
@@ -2774,7 +3813,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 18m</t>
+          <t>1d 15h 56m</t>
         </is>
       </c>
     </row>
@@ -2815,14 +3854,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2887,14 +3926,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -3323,6 +4362,341 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1382962</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Yubraj Biphute</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:31 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:40:21 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:31 PM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381122</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Arbin Thakur</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:07:58 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:19:57 AM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:07:58 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1383657</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Sujal Shrestha</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:33 PM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:01:37 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:33 PM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381219</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:35:16 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1382043</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Manoj Budhathoki</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 07:47:21 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 5m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -512,7 +512,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -2748,10 +2748,8 @@
           <t>Yubraj Biphute</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9705259533</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9705259533</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -2841,10 +2839,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2851,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -2951,10 +2947,8 @@
           <t>Arbin Thakur</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9802100149</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9802100149</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -2989,10 +2983,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.65685</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.65685</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3048,25 +3040,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3448</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.34480000000001</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3162,10 +3150,8 @@
           <t>Sujal Shrestha</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9863481720</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9863481720</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3255,10 +3241,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3269,7 +3253,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3365,10 +3349,8 @@
           <t>Kiran Khadka</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9843560015</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9843560015</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3403,10 +3385,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.71774</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.71774</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3462,25 +3442,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.3018</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.3018</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3576,10 +3552,8 @@
           <t>Manoj Budhathoki</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9803166523</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9803166523</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3614,10 +3588,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.705262</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.705262</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3673,48 +3645,454 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB286</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.305828</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.30582800000001</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 5m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>stb collection</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376366</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:47:02 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 08:58:40 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:26:11 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.64958</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Mahalaxmi-4, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>dilbdr123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L49-7</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.34428</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 39m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>7d 17h 27m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382665</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9840562307</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9844208629</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Radheradhe, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9844208629@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>10:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L61-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 5m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW17" s="3" t="inlineStr">
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3731,7 +4109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3768,7 +4146,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -3778,7 +4156,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3789,7 +4167,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -3801,7 +4179,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 41m</t>
+          <t>4h 16m</t>
         </is>
       </c>
     </row>
@@ -3813,7 +4191,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 56m</t>
+          <t>1d 14h 32m</t>
         </is>
       </c>
     </row>
@@ -3854,14 +4232,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -3926,14 +4304,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4773,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -4462,7 +4840,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -4529,7 +4907,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -4596,7 +4974,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -4663,14 +5041,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>30 Oct 2026 01:52:46 PM</t>
@@ -4694,6 +5072,73 @@
       <c r="M29" s="5" t="inlineStr">
         <is>
           <t>1d 6h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382665</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,14 +511,14 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -3745,20 +3745,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Dil Bahadur Shrestha</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841497101</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841497101</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3793,10 +3787,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.64958</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.64958</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -3848,25 +3840,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L49-7</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.34428</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.34428</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -3962,10 +3950,8 @@
           <t>Hemanta bhandari</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9840562307</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9840562307</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4055,10 +4041,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4069,32 +4053,243 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:38 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382732</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Sumit Tamang</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Sumit Tamang</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9861966412</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9861966412</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:36:53 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.680025</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Near by Sagarmata tole gate, Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>9861966412@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L20-3</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.370184</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>1d 28m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -4109,13 +4304,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -4146,7 +4341,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -4156,7 +4351,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -4167,7 +4362,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4374,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 16m</t>
+          <t>3h 54m</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4386,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 32m</t>
+          <t>1d 13h 19m</t>
         </is>
       </c>
     </row>
@@ -4244,310 +4439,217 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>73.3%</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
       <c r="C16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1381154</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Anil Kumar</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 11:45:39 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>2d 16m</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1381073</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Sagar Dhungana</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:40:01 AM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>2d 1h 57m</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TKT1381073</t>
+          <t>TKT1381154</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sagar Dhungana</t>
+          <t>Anil Kumar</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4577,22 +4679,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
+          <t>30 Oct 2026 12:02:07 PM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:40:01 AM</t>
+          <t>28 Oct 2026 11:45:39 AM</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
+          <t>30 Oct 2026 12:02:07 PM</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4602,19 +4704,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 57m</t>
+          <t>2d 16m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1381027</t>
+          <t>TKT1381073</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Suresh Shrestha</t>
+          <t>Sagar Dhungana</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -4644,22 +4746,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:27:50 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:04:31 AM</t>
+          <t>28 Oct 2026 10:40:01 AM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:27:50 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -4669,19 +4771,19 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>2d 3h 23m</t>
+          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1381392</t>
+          <t>TKT1381073</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Ambar  kumar magar</t>
+          <t>Sagar Dhungana</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4696,12 +4798,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -4711,44 +4813,44 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:39:15 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:39:15 PM</t>
+          <t>28 Oct 2026 10:40:01 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:36:54 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 57m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 57m</t>
+          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1382962</t>
+          <t>TKT1381027</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Yubraj Biphute</t>
+          <t>Suresh Shrestha</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4778,22 +4880,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:31 PM</t>
+          <t>30 Oct 2026 01:27:50 PM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 04:40:21 PM</t>
+          <t>28 Oct 2026 10:04:31 AM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:31 PM</t>
+          <t>30 Oct 2026 01:27:50 PM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4803,19 +4905,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>21h 31m</t>
+          <t>2d 3h 23m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1381122</t>
+          <t>TKT1381392</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Arbin Thakur</t>
+          <t>Ambar  kumar magar</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4830,12 +4932,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4845,44 +4947,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:07:58 PM</t>
+          <t>28 Oct 2026 02:39:15 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:19:57 AM</t>
+          <t>28 Oct 2026 02:39:15 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:07:58 PM</t>
+          <t>30 Oct 2026 01:36:54 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 57m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 48m</t>
+          <t>1d 22h 57m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1383657</t>
+          <t>TKT1382962</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sujal Shrestha</t>
+          <t>Yubraj Biphute</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4912,22 +5014,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:33 PM</t>
+          <t>30 Oct 2026 02:11:31 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:01:37 PM</t>
+          <t>29 Oct 2026 04:40:21 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:33 PM</t>
+          <t>30 Oct 2026 02:11:31 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4937,19 +5039,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1h 9m</t>
+          <t>21h 31m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1381219</t>
+          <t>TKT1381122</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Kiran Khadka</t>
+          <t>Arbin Thakur</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4979,22 +5081,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:53:29 PM</t>
+          <t>30 Oct 2026 02:07:58 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:35:16 PM</t>
+          <t>28 Oct 2026 11:19:57 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:53:29 PM</t>
+          <t>30 Oct 2026 02:07:58 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -5004,19 +5106,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 18m</t>
+          <t>2d 2h 48m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1382043</t>
+          <t>TKT1383657</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Manoj Budhathoki</t>
+          <t>Sujal Shrestha</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5046,22 +5148,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:52:46 PM</t>
+          <t>30 Oct 2026 02:11:33 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 07:47:21 AM</t>
+          <t>30 Oct 2026 01:01:37 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:52:46 PM</t>
+          <t>30 Oct 2026 02:11:33 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5071,74 +5173,275 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 5m</t>
+          <t>1h 9m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>TKT1381219</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:35:16 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1382043</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Manoj Budhathoki</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 07:47:21 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>TKT1382665</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Hemanta bhandari</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>30 Oct 2026 02:11:18 PM</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>29 Oct 2026 01:42:26 PM</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>30 Oct 2026 02:11:18 PM</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>1d 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1382732</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Sumit Tamang</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:36:53 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4139,20 +4139,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Sumit Tamang</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9861966412</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9861966412</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4187,10 +4181,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.680025</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.680025</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4246,25 +4238,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L20-3</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.370184</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.37018399999999</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4313,7 +4301,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5411,7 +5399,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4281,6 +4281,404 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 3:17 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382760</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Tamang</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Tamang</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9843358659</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9843358659</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:07:01 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>imadol near bhandari marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>10:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L55-2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 10m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 3:44 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>no internet conncetion</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382964</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Poudel</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Poudel</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>8549856548</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:44:40 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9746291665</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:44:40 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>P9Q7+J3 Budhanilkantha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>09:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>23h 2m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4292,7 +4690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4301,7 +4699,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4329,7 +4727,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4339,7 +4737,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -4350,7 +4748,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4760,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 54m</t>
+          <t>3h 21m</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4772,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 19m</t>
+          <t>1d 11h 22m</t>
         </is>
       </c>
     </row>
@@ -4415,14 +4813,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -4445,333 +4843,240 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>73.3%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1381154</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Anil Kumar</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 11:45:39 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>2d 16m</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1381073</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Sagar Dhungana</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:40:01 AM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>2d 1h 57m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1381073</t>
+          <t>TKT1381154</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Sagar Dhungana</t>
+          <t>Anil Kumar</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4801,22 +5106,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
+          <t>30 Oct 2026 12:02:07 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:40:01 AM</t>
+          <t>28 Oct 2026 11:45:39 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
+          <t>30 Oct 2026 12:02:07 PM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -4826,19 +5131,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 57m</t>
+          <t>2d 16m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1381027</t>
+          <t>TKT1381073</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Suresh Shrestha</t>
+          <t>Sagar Dhungana</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4868,22 +5173,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:27:50 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:04:31 AM</t>
+          <t>28 Oct 2026 10:40:01 AM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:27:50 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4893,19 +5198,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>2d 3h 23m</t>
+          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1381392</t>
+          <t>TKT1381073</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Ambar  kumar magar</t>
+          <t>Sagar Dhungana</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4920,12 +5225,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4935,44 +5240,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:39:15 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:39:15 PM</t>
+          <t>28 Oct 2026 10:40:01 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:36:54 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 57m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 57m</t>
+          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1382962</t>
+          <t>TKT1381027</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Yubraj Biphute</t>
+          <t>Suresh Shrestha</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -5002,22 +5307,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:31 PM</t>
+          <t>30 Oct 2026 01:27:50 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 04:40:21 PM</t>
+          <t>28 Oct 2026 10:04:31 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:31 PM</t>
+          <t>30 Oct 2026 01:27:50 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -5027,19 +5332,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>21h 31m</t>
+          <t>2d 3h 23m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1381122</t>
+          <t>TKT1381392</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Arbin Thakur</t>
+          <t>Ambar  kumar magar</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5054,12 +5359,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -5069,44 +5374,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:07:58 PM</t>
+          <t>28 Oct 2026 02:39:15 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:19:57 AM</t>
+          <t>28 Oct 2026 02:39:15 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:07:58 PM</t>
+          <t>30 Oct 2026 01:36:54 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 57m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 48m</t>
+          <t>1d 22h 57m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1383657</t>
+          <t>TKT1382962</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sujal Shrestha</t>
+          <t>Yubraj Biphute</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5136,22 +5441,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:33 PM</t>
+          <t>30 Oct 2026 02:11:31 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:01:37 PM</t>
+          <t>29 Oct 2026 04:40:21 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:33 PM</t>
+          <t>30 Oct 2026 02:11:31 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5161,19 +5466,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1h 9m</t>
+          <t>21h 31m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1381219</t>
+          <t>TKT1381122</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Kiran Khadka</t>
+          <t>Arbin Thakur</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5203,22 +5508,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:53:29 PM</t>
+          <t>30 Oct 2026 02:07:58 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:35:16 PM</t>
+          <t>28 Oct 2026 11:19:57 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:53:29 PM</t>
+          <t>30 Oct 2026 02:07:58 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5228,19 +5533,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 18m</t>
+          <t>2d 2h 48m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1382043</t>
+          <t>TKT1383657</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Manoj Budhathoki</t>
+          <t>Sujal Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5270,22 +5575,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:52:46 PM</t>
+          <t>30 Oct 2026 02:11:33 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 07:47:21 AM</t>
+          <t>30 Oct 2026 01:01:37 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:52:46 PM</t>
+          <t>30 Oct 2026 02:11:33 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5295,19 +5600,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 5m</t>
+          <t>1h 9m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1382665</t>
+          <t>TKT1381219</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Hemanta bhandari</t>
+          <t>Kiran Khadka</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5337,22 +5642,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:18 PM</t>
+          <t>30 Oct 2026 01:53:29 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 01:42:26 PM</t>
+          <t>28 Oct 2026 12:35:16 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:18 PM</t>
+          <t>30 Oct 2026 01:53:29 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5362,74 +5667,342 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 28m</t>
+          <t>2d 1h 18m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>TKT1382043</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Manoj Budhathoki</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 07:47:21 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382665</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>TKT1382732</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Sumit Tamang</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>30 Oct 2026 02:38:52 PM</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 02:36:53 PM</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>30 Oct 2026 02:38:52 PM</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>1d 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382760</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Tamang</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:07:01 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1d 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1382964</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Shristi Poudel</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:44:40 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:44:40 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>23h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4348,10 +4348,8 @@
           <t>Raj Kumar Tamang</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9843358659</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9843358659</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4437,10 +4435,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4451,7 +4447,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4547,10 +4543,8 @@
           <t>Shristi Poudel</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>8549856548</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>8549856548</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4636,10 +4630,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4650,7 +4642,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4699,7 +4691,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5905,7 +5897,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -5972,7 +5964,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4671,6 +4671,213 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 4:02 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>slow speed</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379469</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Aayush Shrestha</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Aayush Shrestha</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9849396345</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 10:48:04 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9849396345</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:40 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 04:02:11 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.67544</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Patan, Ombahal Bangalamukhi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>uraayush@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB604E</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.32756</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>5h 14m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4682,11 +4889,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -4719,7 +4926,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4740,7 +4947,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -4853,109 +5060,104 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -4971,238 +5173,150 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1381154</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Anil Kumar</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 11:45:39 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:02:07 PM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>2d 16m</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1381073</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Sagar Dhungana</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:40:01 AM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>2d 1h 57m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1381073</t>
+          <t>TKT1381154</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sagar Dhungana</t>
+          <t>Anil Kumar</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -5232,22 +5346,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
+          <t>30 Oct 2026 12:02:07 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:40:01 AM</t>
+          <t>28 Oct 2026 11:45:39 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 12:37:49 PM</t>
+          <t>30 Oct 2026 12:02:07 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -5257,19 +5371,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 57m</t>
+          <t>2d 16m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1381027</t>
+          <t>TKT1381073</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Suresh Shrestha</t>
+          <t>Sagar Dhungana</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -5299,22 +5413,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:27:50 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:04:31 AM</t>
+          <t>28 Oct 2026 10:40:01 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:27:50 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -5324,19 +5438,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>2d 3h 23m</t>
+          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1381392</t>
+          <t>TKT1381073</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Ambar  kumar magar</t>
+          <t>Sagar Dhungana</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5351,12 +5465,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -5366,44 +5480,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:39:15 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:39:15 PM</t>
+          <t>28 Oct 2026 10:40:01 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:36:54 PM</t>
+          <t>30 Oct 2026 12:37:49 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 57m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 57m</t>
+          <t>2d 1h 57m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1382962</t>
+          <t>TKT1381027</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Yubraj Biphute</t>
+          <t>Suresh Shrestha</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5433,22 +5547,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:31 PM</t>
+          <t>30 Oct 2026 01:27:50 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 04:40:21 PM</t>
+          <t>28 Oct 2026 10:04:31 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:31 PM</t>
+          <t>30 Oct 2026 01:27:50 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5458,19 +5572,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>21h 31m</t>
+          <t>2d 3h 23m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1381122</t>
+          <t>TKT1381392</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Arbin Thakur</t>
+          <t>Ambar  kumar magar</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5485,12 +5599,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5500,44 +5614,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:07:58 PM</t>
+          <t>28 Oct 2026 02:39:15 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:19:57 AM</t>
+          <t>28 Oct 2026 02:39:15 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:07:58 PM</t>
+          <t>30 Oct 2026 01:36:54 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 57m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 48m</t>
+          <t>1d 22h 57m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1383657</t>
+          <t>TKT1382962</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sujal Shrestha</t>
+          <t>Yubraj Biphute</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5567,22 +5681,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:33 PM</t>
+          <t>30 Oct 2026 02:11:31 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:01:37 PM</t>
+          <t>29 Oct 2026 04:40:21 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:33 PM</t>
+          <t>30 Oct 2026 02:11:31 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5592,19 +5706,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1h 9m</t>
+          <t>21h 31m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1381219</t>
+          <t>TKT1381122</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Kiran Khadka</t>
+          <t>Arbin Thakur</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5634,22 +5748,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:53:29 PM</t>
+          <t>30 Oct 2026 02:07:58 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:35:16 PM</t>
+          <t>28 Oct 2026 11:19:57 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:53:29 PM</t>
+          <t>30 Oct 2026 02:07:58 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5659,19 +5773,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 18m</t>
+          <t>2d 2h 48m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1382043</t>
+          <t>TKT1383657</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Manoj Budhathoki</t>
+          <t>Sujal Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -5701,22 +5815,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:52:46 PM</t>
+          <t>30 Oct 2026 02:11:33 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 07:47:21 AM</t>
+          <t>30 Oct 2026 01:01:37 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 01:52:46 PM</t>
+          <t>30 Oct 2026 02:11:33 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5726,19 +5840,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 5m</t>
+          <t>1h 9m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1382665</t>
+          <t>TKT1381219</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Hemanta bhandari</t>
+          <t>Kiran Khadka</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5768,22 +5882,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:18 PM</t>
+          <t>30 Oct 2026 01:53:29 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 01:42:26 PM</t>
+          <t>28 Oct 2026 12:35:16 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:11:18 PM</t>
+          <t>30 Oct 2026 01:53:29 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5793,29 +5907,29 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 28m</t>
+          <t>2d 1h 18m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1382732</t>
+          <t>TKT1382043</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sumit Tamang</t>
+          <t>Manoj Budhathoki</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -5835,22 +5949,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:38:52 PM</t>
+          <t>30 Oct 2026 01:52:46 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>29 Oct 2026 02:36:53 PM</t>
+          <t>29 Oct 2026 07:47:21 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>30 Oct 2026 02:38:52 PM</t>
+          <t>30 Oct 2026 01:52:46 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -5860,19 +5974,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 1m</t>
+          <t>1d 6h 5m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1382760</t>
+          <t>TKT1382665</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Raj Kumar Tamang</t>
+          <t>Hemanta bhandari</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -5902,22 +6016,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 03:17:16 PM</t>
+          <t>30 Oct 2026 02:11:18 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>29 Oct 2026 03:07:01 PM</t>
+          <t>29 Oct 2026 01:42:26 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>30 Oct 2026 03:17:16 PM</t>
+          <t>30 Oct 2026 02:11:18 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -5927,72 +6041,206 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 10m</t>
+          <t>1d 28m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>TKT1382732</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Sumit Tamang</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:36:53 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382760</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Tamang</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:07:01 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1d 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>TKT1382964</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Shristi Poudel</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>No Internet Connection</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Configuration Issue</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>30 Oct 2026 03:44:40 PM</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>29 Oct 2026 04:42:09 PM</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>30 Oct 2026 03:44:40 PM</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>23h 2m</t>
         </is>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4738,10 +4738,8 @@
           <t>Aayush Shrestha</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9849396345</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9849396345</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4776,10 +4774,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.67544</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.67544</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -4831,25 +4827,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB604E</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.32756</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.32756000000001</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4870,6 +4870,420 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 9:31 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382779</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Januka Puri</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Januka Puri</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9845865646</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:31:38 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9841385524</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:24:10 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:31:38 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.67952</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Pimbhal cooker cafe House No. 191, M8FC+WXW, Dhaugal Galli Pimbahal, Lalitpur 44700, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>14:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.30697</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 7m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 9:30 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382482</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Bahadur KC</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Bahadur KC</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9801026714</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:30:41 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9801026714</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:34:03 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:30:41 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.659728</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Anu Books Store - Book store Lagankhel Satdobato Rd Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>18:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB956</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.323702</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>1d 9h 56m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4881,7 +5295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4890,7 +5304,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4918,7 +5332,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4928,7 +5342,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -4939,7 +5353,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4951,7 +5365,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 21m</t>
+          <t>2h 56m</t>
         </is>
       </c>
     </row>
@@ -4963,7 +5377,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 11h 22m</t>
+          <t>1d 10h 57m</t>
         </is>
       </c>
     </row>
@@ -5004,14 +5418,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -5130,14 +5544,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -6238,6 +6652,140 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382779</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Januka Puri</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:31:38 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:24:10 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:31:38 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1382482</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Kamal Bahadur KC</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:30:41 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:34:03 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:30:41 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>1d 9h 56m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_30_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_30_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4937,10 +4937,8 @@
           <t>Januka Puri</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9845865646</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9845865646</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -4975,10 +4973,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.67952</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.67952</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5030,25 +5026,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.30697</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.30697000000001</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5144,10 +5136,8 @@
           <t>Kamal Bahadur KC</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9801026714</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9801026714</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5182,10 +5172,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.659728</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.659728</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5237,25 +5225,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB956</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.323702</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.323702</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5304,7 +5288,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6685,7 +6669,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -6752,7 +6736,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
